--- a/01_Input/00_CO Validation/Malawi - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Malawi - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="292" documentId="11_C6A8EC944518ADD515B964CEBC08252D554BC346" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{903639D4-708B-491E-BE32-F69325C48BF0}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="11_C6A8EC944518ADD515B964CEBC08252D554BC346" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF5D50BE-D233-4853-9377-9D17E21AD95B}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="101">
   <si>
     <t>Project ID</t>
   </si>
@@ -174,40 +177,43 @@
     <t>GHG Emission Reduction</t>
   </si>
   <si>
+    <t>Greenhouse gas emissions mitigated GtCO2</t>
+  </si>
+  <si>
+    <t>1068 metric tons of carbon dioxide equivalent (Units of measure: metric tons of CO2e)</t>
+  </si>
+  <si>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of direct beneficiaries disaggregated by gender (and customer segment) as co-benefit of GEF investment </t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>Entrepreneurship Training</t>
+  </si>
+  <si>
+    <t>Number of direct primary jobs created in the minigrid sector, disaggregated by gender, for minigrid development, operation and productive use</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>to the CO: What is a "Productive User"?</t>
+  </si>
+  <si>
+    <t>to the CO: Please estimate number of beneficiaries.</t>
+  </si>
+  <si>
+    <t>GHG Emissions Reduction</t>
+  </si>
+  <si>
     <t xml:space="preserve">Greenhouse gas emissions mitigated </t>
-  </si>
-  <si>
-    <t>1068 metric tons of carbon dioxide equivalent (Units of measure: metric tons of CO2e)</t>
-  </si>
-  <si>
-    <t>GEF</t>
-  </si>
-  <si>
-    <t>VF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of direct beneficiaries disaggregated by gender (and customer segment) as co-benefit of GEF investment </t>
-  </si>
-  <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
-  </si>
-  <si>
-    <t>Number of direct primary jobs created in the minigrid sector, disaggregated by gender, for minigrid development, operation and productive use</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>to the CO: What is a "Productive User"?</t>
-  </si>
-  <si>
-    <t>to the CO: Please estimate number of beneficiaries.</t>
-  </si>
-  <si>
-    <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <t>to the CO: Please provide a unit</t>
@@ -639,7 +645,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -768,13 +774,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -809,6 +818,32 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1128,16 +1163,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -1152,7 +1187,7 @@
       <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="52" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
@@ -1185,31 +1220,31 @@
       <c r="S1" s="19"/>
     </row>
     <row r="2" spans="1:19" ht="60.75">
-      <c r="A2" s="31">
+      <c r="A2" s="36">
         <v>126170</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="54" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="31">
         <v>3379000</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="69">
         <v>0.38500000000000001</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="69">
         <v>2.0249999999999999</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="70" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="30" t="s">
@@ -1232,23 +1267,23 @@
       <c r="S2" s="19"/>
     </row>
     <row r="3" spans="1:19" ht="60.75">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="46" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="I3" s="70" t="s">
         <v>31</v>
       </c>
       <c r="J3" s="30"/>
@@ -1268,22 +1303,22 @@
     </row>
     <row r="4" spans="1:19" ht="121.5">
       <c r="A4" s="38"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="47" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="69">
         <v>0</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="72">
         <v>15</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="70" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="30"/>
@@ -1303,20 +1338,20 @@
     </row>
     <row r="5" spans="1:19" ht="45.75">
       <c r="A5" s="38"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="47" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="28">
+      <c r="G5" s="69"/>
+      <c r="H5" s="72">
         <v>10000</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="70" t="s">
         <v>37</v>
       </c>
       <c r="J5" s="30"/>
@@ -1332,18 +1367,18 @@
     </row>
     <row r="6" spans="1:19" ht="45.75">
       <c r="A6" s="38"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="47" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="71" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27">
+      <c r="F6" s="73"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69">
         <v>210000</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="70" t="s">
         <v>39</v>
       </c>
       <c r="J6" s="30"/>
@@ -1360,17 +1395,17 @@
       <c r="S6" s="19"/>
     </row>
     <row r="7" spans="1:19" ht="91.5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="46" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="48" t="s">
+      <c r="F7" s="73"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70" t="s">
         <v>42</v>
       </c>
       <c r="J7" s="30"/>
@@ -1393,31 +1428,31 @@
       <c r="S7" s="19"/>
     </row>
     <row r="8" spans="1:19" ht="45.75">
-      <c r="A8" s="32">
+      <c r="A8" s="36">
         <v>6512</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="31">
         <v>396125</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="69">
         <v>0</v>
       </c>
-      <c r="H8" s="27">
-        <v>1068</v>
-      </c>
-      <c r="I8" s="52" t="s">
+      <c r="H8" s="69">
+        <v>1.0680000000000001</v>
+      </c>
+      <c r="I8" s="70" t="s">
         <v>48</v>
       </c>
       <c r="J8" s="30" t="s">
@@ -1436,23 +1471,23 @@
       <c r="S8" s="19"/>
     </row>
     <row r="9" spans="1:19" ht="91.5">
-      <c r="A9" s="36"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="46" t="s">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="69">
         <v>0</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="75">
         <v>763</v>
       </c>
-      <c r="I9" s="54"/>
+      <c r="I9" s="76"/>
       <c r="J9" s="30"/>
       <c r="K9" s="23">
         <v>0.51</v>
@@ -1474,22 +1509,22 @@
     </row>
     <row r="10" spans="1:19" ht="121.5">
       <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="46" t="s">
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="69">
         <v>0</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="75">
         <v>10</v>
       </c>
-      <c r="I10" s="54"/>
+      <c r="I10" s="76"/>
       <c r="J10" s="30"/>
       <c r="K10" s="23">
         <v>0.5</v>
@@ -1816,7 +1851,7 @@
         <v>58</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G8" s="27">
         <v>0</v>
@@ -1827,15 +1862,15 @@
       <c r="I8" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="55" t="s">
+      <c r="J8" s="56" t="s">
         <v>49</v>
       </c>
       <c r="K8" s="19"/>
-      <c r="L8" s="55" t="s">
+      <c r="L8" s="56" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="91.5">
@@ -1856,11 +1891,11 @@
         <v>763</v>
       </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="56"/>
+      <c r="J9" s="57"/>
       <c r="K9" s="23">
         <v>0.51</v>
       </c>
-      <c r="L9" s="56"/>
+      <c r="L9" s="57"/>
       <c r="M9" s="19"/>
       <c r="O9" t="s">
         <v>32</v>
@@ -1890,11 +1925,11 @@
         <v>10</v>
       </c>
       <c r="I10" s="16"/>
-      <c r="J10" s="57"/>
+      <c r="J10" s="58"/>
       <c r="K10" s="23">
         <v>0.5</v>
       </c>
-      <c r="L10" s="57"/>
+      <c r="L10" s="58"/>
       <c r="M10" s="19"/>
     </row>
   </sheetData>
@@ -1984,45 +2019,45 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="60.75">
-      <c r="A2" s="58">
+      <c r="A2" s="59">
         <v>126170</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="59">
         <v>3379000</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60.75">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="59"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="60"/>
       <c r="E3" s="2"/>
       <c r="F3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H3" s="11">
         <v>10000</v>
@@ -2032,10 +2067,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="60.75">
-      <c r="A4" s="59"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="59"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="60"/>
       <c r="E4" s="2"/>
       <c r="F4" s="6" t="s">
         <v>33</v>
@@ -2049,13 +2084,13 @@
       <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:10" ht="60.75">
-      <c r="A5" s="59"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="59"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="60"/>
       <c r="E5" s="2"/>
       <c r="F5" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
@@ -2066,10 +2101,10 @@
       <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="59"/>
+      <c r="A6" s="60"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
@@ -2077,14 +2112,14 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="91.5">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="59"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="60"/>
       <c r="E7" s="2" t="s">
         <v>41</v>
       </c>
@@ -2109,10 +2144,10 @@
         <v>396125</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G8" s="8">
         <v>0</v>
@@ -2136,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" t="s">
@@ -2145,7 +2180,7 @@
     </row>
     <row r="10" spans="1:10" ht="121.5">
       <c r="E10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>54</v>
@@ -2154,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" t="s">
@@ -2197,160 +2232,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="62" t="s">
-        <v>73</v>
+      <c r="A2" s="63" t="s">
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="62"/>
+      <c r="A3" s="63"/>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="62"/>
+      <c r="A4" s="63"/>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="63" t="s">
-        <v>78</v>
+      <c r="A5" s="64" t="s">
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="63"/>
+      <c r="A6" s="64"/>
       <c r="B6" t="s">
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="63"/>
+      <c r="A7" s="64"/>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="63"/>
+      <c r="A8" s="64"/>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="63"/>
+      <c r="A9" s="64"/>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="64" t="s">
-        <v>87</v>
+      <c r="A10" s="65" t="s">
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="64"/>
+      <c r="A11" s="65"/>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="65" t="s">
-        <v>91</v>
+      <c r="A12" s="66" t="s">
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="65"/>
+      <c r="A13" s="66"/>
       <c r="B13" t="s">
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="65"/>
+      <c r="A14" s="66"/>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Malawi - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Malawi - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28224"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="345" documentId="11_C6A8EC944518ADD515B964CEBC08252D554BC346" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{415E45DB-7BBA-4597-9B1C-61A5BC9AEE11}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="11_C6A8EC944518ADD515B964CEBC08252D554BC346" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F7E8156-C252-48CF-BC52-2350E85AF575}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -2621,8 +2621,85 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Challa Getachew</DisplayName>
+        <AccountId>1900</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shigeki Komatsubara</DisplayName>
+        <AccountId>1901</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Azhar Malik</DisplayName>
+        <AccountId>1902</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Charles Nyandiga</DisplayName>
+        <AccountId>94</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Fungai Matura</DisplayName>
+        <AccountId>1028</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Shamiso Kacelenga</DisplayName>
+        <AccountId>1415</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Mathangeni Ngwira</DisplayName>
+        <AccountId>1509</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Rabi Narayan Gaudo</DisplayName>
+        <AccountId>1866</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2647,6 +2724,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2726,6 +2804,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2869,85 +2952,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Challa Getachew</DisplayName>
-        <AccountId>1900</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shigeki Komatsubara</DisplayName>
-        <AccountId>1901</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Azhar Malik</DisplayName>
-        <AccountId>1902</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Charles Nyandiga</DisplayName>
-        <AccountId>94</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Fungai Matura</DisplayName>
-        <AccountId>1028</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Shamiso Kacelenga</DisplayName>
-        <AccountId>1415</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Mathangeni Ngwira</DisplayName>
-        <AccountId>1509</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Rabi Narayan Gaudo</DisplayName>
-        <AccountId>1866</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04C5E1DE-478E-4779-A6C3-B5E5D8AF9F4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E91D03AA-E64C-4937-8935-3E5E4B79F456}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2955,5 +2961,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E91D03AA-E64C-4937-8935-3E5E4B79F456}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71CAE28C-887D-495B-B6ED-22C18DE9F226}"/>
 </file>
--- a/01_Input/00_CO Validation/Malawi - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Malawi - Energy Projects.xlsx
@@ -526,10 +526,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -614,6 +614,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1675,15 +1695,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="28" t="n">
+      <c r="K11" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="80" t="n"/>
-      <c r="M11" s="81" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L11" s="81" t="n"/>
+      <c r="M11" s="60" t="n"/>
       <c r="N11" s="28" t="n"/>
       <c r="O11" s="21" t="n"/>
       <c r="P11" s="61" t="n"/>
@@ -1705,7 +1721,7 @@
       <c r="AG11" s="17" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="15">
+  <dataValidations count="13">
     <dataValidation sqref="AD2:AD10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -1745,17 +1761,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
